--- a/Team-Data/2013-14/2-23-2013-14.xlsx
+++ b/Team-Data/2013-14/2-23-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,22 +806,22 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>17</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH2" t="n">
         <v>10</v>
       </c>
       <c r="AI2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
         <v>21</v>
@@ -775,10 +842,10 @@
         <v>20</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
@@ -808,13 +875,13 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -921,10 +988,10 @@
         <v>-3.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
         <v>27</v>
@@ -936,7 +1003,7 @@
         <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ3" t="n">
         <v>11</v>
@@ -957,7 +1024,7 @@
         <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
         <v>12</v>
@@ -966,7 +1033,7 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
         <v>14</v>
@@ -978,13 +1045,13 @@
         <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
         <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
         <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.481</v>
+        <v>0.472</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1046,46 +1113,46 @@
         <v>78.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M4" t="n">
         <v>21.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.365</v>
+        <v>0.362</v>
       </c>
       <c r="O4" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0.762</v>
       </c>
       <c r="R4" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T4" t="n">
         <v>39</v>
       </c>
       <c r="U4" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V4" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y4" t="n">
         <v>4.1</v>
@@ -1094,25 +1161,25 @@
         <v>21.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AD4" t="n">
         <v>29</v>
       </c>
       <c r="AE4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF4" t="n">
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
         <v>8</v>
@@ -1127,7 +1194,7 @@
         <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM4" t="n">
         <v>14</v>
@@ -1136,16 +1203,16 @@
         <v>12</v>
       </c>
       <c r="AO4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
         <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS4" t="n">
         <v>27</v>
@@ -1154,10 +1221,10 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
         <v>13</v>
@@ -1178,7 +1245,7 @@
         <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
         <v>18</v>
@@ -1327,7 +1394,7 @@
         <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
         <v>7</v>
@@ -1336,7 +1403,7 @@
         <v>21</v>
       </c>
       <c r="AU5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -1389,67 +1456,67 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" t="n">
         <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>0.527</v>
+        <v>0.537</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="J6" t="n">
         <v>80.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.427</v>
+        <v>0.428</v>
       </c>
       <c r="L6" t="n">
         <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="O6" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="R6" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S6" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T6" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="U6" t="n">
         <v>22.3</v>
       </c>
       <c r="V6" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W6" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
         <v>6.3</v>
@@ -1458,22 +1525,22 @@
         <v>19.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.5</v>
+        <v>92.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1509,10 +1576,10 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -1524,7 +1591,7 @@
         <v>26</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
         <v>7</v>
@@ -1533,16 +1600,16 @@
         <v>29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
         <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -1571,85 +1638,85 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" t="n">
         <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>0.386</v>
+        <v>0.393</v>
       </c>
       <c r="H7" t="n">
         <v>48.8</v>
       </c>
       <c r="I7" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J7" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K7" t="n">
         <v>0.424</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M7" t="n">
         <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.351</v>
+        <v>0.355</v>
       </c>
       <c r="O7" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P7" t="n">
         <v>23.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.745</v>
+        <v>0.743</v>
       </c>
       <c r="R7" t="n">
         <v>12.8</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T7" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U7" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V7" t="n">
         <v>14.5</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AA7" t="n">
         <v>20.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.7</v>
+        <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
@@ -1664,7 +1731,7 @@
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AJ7" t="n">
         <v>5</v>
@@ -1673,13 +1740,13 @@
         <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
         <v>15</v>
@@ -1688,13 +1755,13 @@
         <v>15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
@@ -1703,16 +1770,16 @@
         <v>27</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AY7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ7" t="n">
         <v>14</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1852,10 +1919,10 @@
         <v>13</v>
       </c>
       <c r="AK8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
@@ -1882,13 +1949,13 @@
         <v>28</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
         <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
         <v>24</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -1935,55 +2002,55 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>0.455</v>
+        <v>0.463</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J9" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.445</v>
+        <v>0.447</v>
       </c>
       <c r="L9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.362</v>
+        <v>0.359</v>
       </c>
       <c r="O9" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P9" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.72</v>
+        <v>0.721</v>
       </c>
       <c r="R9" t="n">
         <v>12.3</v>
       </c>
       <c r="S9" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T9" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U9" t="n">
         <v>21.8</v>
@@ -1992,34 +2059,34 @@
         <v>15.5</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA9" t="n">
         <v>21.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
         <v>19</v>
@@ -2037,7 +2104,7 @@
         <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2046,7 +2113,7 @@
         <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
         <v>6</v>
@@ -2070,16 +2137,16 @@
         <v>25</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2088,7 +2155,7 @@
         <v>11</v>
       </c>
       <c r="BC9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
@@ -2222,7 +2289,7 @@
         <v>27</v>
       </c>
       <c r="AM10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN10" t="n">
         <v>29</v>
@@ -2246,10 +2313,10 @@
         <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW10" t="n">
         <v>3</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -2377,19 +2444,19 @@
         <v>4.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
@@ -2401,7 +2468,7 @@
         <v>9</v>
       </c>
       <c r="AL11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
@@ -2416,10 +2483,10 @@
         <v>20</v>
       </c>
       <c r="AQ11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -2481,85 +2548,85 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12" t="n">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.679</v>
+        <v>0.673</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J12" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L12" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="N12" t="n">
         <v>0.353</v>
       </c>
       <c r="O12" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="P12" t="n">
         <v>31.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S12" t="n">
         <v>34.1</v>
       </c>
       <c r="T12" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U12" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V12" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W12" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X12" t="n">
         <v>5.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
         <v>20.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.1</v>
+        <v>105.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2571,25 +2638,25 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
       </c>
       <c r="AK12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL12" t="n">
         <v>4</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>6</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2601,7 +2668,7 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
@@ -2622,10 +2689,10 @@
         <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>7.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2750,10 +2817,10 @@
         <v>1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
         <v>21</v>
@@ -2771,7 +2838,7 @@
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
@@ -2798,7 +2865,7 @@
         <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.655</v>
+        <v>0.649</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2866,22 +2933,22 @@
         <v>81.59999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.472</v>
+        <v>0.471</v>
       </c>
       <c r="L14" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O14" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="P14" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="Q14" t="n">
         <v>0.727</v>
@@ -2908,16 +2975,16 @@
         <v>4.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Z14" t="n">
         <v>21.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.1</v>
+        <v>106.7</v>
       </c>
       <c r="AC14" t="n">
         <v>5.9</v>
@@ -2938,7 +3005,7 @@
         <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
@@ -2947,13 +3014,13 @@
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
         <v>1</v>
@@ -2971,16 +3038,16 @@
         <v>13</v>
       </c>
       <c r="AT14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
       </c>
       <c r="AV14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW14" t="n">
         <v>8</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>9</v>
       </c>
       <c r="AX14" t="n">
         <v>20</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
         <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,16 +3112,16 @@
         <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="K15" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="N15" t="n">
         <v>0.373</v>
@@ -3063,28 +3130,28 @@
         <v>16.8</v>
       </c>
       <c r="P15" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.753</v>
+        <v>0.755</v>
       </c>
       <c r="R15" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T15" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U15" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V15" t="n">
         <v>15.4</v>
       </c>
       <c r="W15" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X15" t="n">
         <v>5.5</v>
@@ -3105,16 +3172,16 @@
         <v>-5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
@@ -3126,13 +3193,13 @@
         <v>10</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="n">
         <v>4</v>
       </c>
       <c r="AM15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN15" t="n">
         <v>8</v>
@@ -3156,7 +3223,7 @@
         <v>22</v>
       </c>
       <c r="AU15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
         <v>22</v>
@@ -3168,10 +3235,10 @@
         <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA15" t="n">
         <v>27</v>
@@ -3180,7 +3247,7 @@
         <v>15</v>
       </c>
       <c r="BC15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3335,7 +3402,7 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3347,13 +3414,13 @@
         <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY16" t="n">
         <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
         <v>30</v>
@@ -3362,7 +3429,7 @@
         <v>27</v>
       </c>
       <c r="BC16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -3391,52 +3458,52 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.741</v>
+        <v>0.736</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J17" t="n">
-        <v>76.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.508</v>
+        <v>0.509</v>
       </c>
       <c r="L17" t="n">
         <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="N17" t="n">
         <v>0.368</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P17" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R17" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="S17" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T17" t="n">
         <v>36.7</v>
@@ -3445,13 +3512,13 @@
         <v>23.5</v>
       </c>
       <c r="V17" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W17" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y17" t="n">
         <v>3</v>
@@ -3460,22 +3527,22 @@
         <v>20.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.1</v>
+        <v>104.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AD17" t="n">
         <v>29</v>
       </c>
       <c r="AE17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF17" t="n">
         <v>3</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
       </c>
       <c r="AG17" t="n">
         <v>3</v>
@@ -3493,13 +3560,13 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM17" t="n">
         <v>13</v>
       </c>
       <c r="AN17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
         <v>13</v>
@@ -3523,7 +3590,7 @@
         <v>6</v>
       </c>
       <c r="AV17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3678,13 +3745,13 @@
         <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN18" t="n">
         <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP18" t="n">
         <v>27</v>
@@ -3723,7 +3790,7 @@
         <v>17</v>
       </c>
       <c r="BB18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" t="n">
         <v>27</v>
       </c>
       <c r="F19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.482</v>
+        <v>0.491</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,7 +3840,7 @@
         <v>38.5</v>
       </c>
       <c r="J19" t="n">
-        <v>87.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="K19" t="n">
         <v>0.438</v>
@@ -3782,43 +3849,43 @@
         <v>7.6</v>
       </c>
       <c r="M19" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="N19" t="n">
         <v>0.345</v>
       </c>
       <c r="O19" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="P19" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="R19" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S19" t="n">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="T19" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="U19" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="V19" t="n">
         <v>13.8</v>
       </c>
       <c r="W19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z19" t="n">
         <v>18.1</v>
@@ -3827,28 +3894,28 @@
         <v>23.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ19" t="n">
         <v>3</v>
@@ -3863,7 +3930,7 @@
         <v>12</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3872,10 +3939,10 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
         <v>8</v>
@@ -3890,7 +3957,7 @@
         <v>7</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
@@ -3908,7 +3975,7 @@
         <v>4</v>
       </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4057,13 +4124,13 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -4197,13 +4264,13 @@
         <v>-1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
         <v>23</v>
@@ -4218,7 +4285,7 @@
         <v>14</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
@@ -4227,7 +4294,7 @@
         <v>6</v>
       </c>
       <c r="AN21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4239,7 +4306,7 @@
         <v>21</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>28</v>
@@ -4272,7 +4339,7 @@
         <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -4301,37 +4368,37 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" t="n">
         <v>43</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22" t="n">
-        <v>0.754</v>
+        <v>0.768</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J22" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0.474</v>
       </c>
       <c r="L22" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O22" t="n">
         <v>19.4</v>
@@ -4346,13 +4413,13 @@
         <v>11</v>
       </c>
       <c r="S22" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="T22" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U22" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V22" t="n">
         <v>15.8</v>
@@ -4364,31 +4431,31 @@
         <v>6.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.8</v>
+        <v>104.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
         <v>26</v>
@@ -4406,10 +4473,10 @@
         <v>17</v>
       </c>
       <c r="AM22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4445,7 +4512,7 @@
         <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E23" t="n">
         <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G23" t="n">
-        <v>0.293</v>
+        <v>0.298</v>
       </c>
       <c r="H23" t="n">
         <v>48.8</v>
@@ -4501,7 +4568,7 @@
         <v>36.5</v>
       </c>
       <c r="J23" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K23" t="n">
         <v>0.442</v>
@@ -4510,16 +4577,16 @@
         <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N23" t="n">
         <v>0.352</v>
       </c>
       <c r="O23" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P23" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q23" t="n">
         <v>0.762</v>
@@ -4528,10 +4595,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T23" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U23" t="n">
         <v>20.8</v>
@@ -4540,25 +4607,25 @@
         <v>14.6</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4579,34 +4646,34 @@
         <v>22</v>
       </c>
       <c r="AJ23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
       </c>
       <c r="AL23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
         <v>23</v>
       </c>
       <c r="AP23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR23" t="n">
         <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
         <v>23</v>
@@ -4615,7 +4682,7 @@
         <v>20</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
@@ -4624,10 +4691,10 @@
         <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4636,7 +4703,7 @@
         <v>24</v>
       </c>
       <c r="BC23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -4743,13 +4810,13 @@
         <v>-10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
       </c>
       <c r="AF24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG24" t="n">
         <v>29</v>
@@ -4785,7 +4852,7 @@
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS24" t="n">
         <v>14</v>
@@ -4803,13 +4870,13 @@
         <v>2</v>
       </c>
       <c r="AX24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
         <v>13</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E25" t="n">
         <v>33</v>
       </c>
       <c r="F25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6</v>
+        <v>0.611</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
@@ -4877,34 +4944,34 @@
         <v>25.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O25" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P25" t="n">
         <v>24.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R25" t="n">
         <v>11.5</v>
       </c>
       <c r="S25" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="T25" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="U25" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="V25" t="n">
         <v>15.2</v>
       </c>
       <c r="W25" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X25" t="n">
         <v>4.9</v>
@@ -4913,19 +4980,19 @@
         <v>4.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA25" t="n">
         <v>21.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.1</v>
+        <v>105</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4934,7 +5001,7 @@
         <v>8</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH25" t="n">
         <v>19</v>
@@ -4949,19 +5016,19 @@
         <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM25" t="n">
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO25" t="n">
         <v>10</v>
       </c>
       <c r="AP25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ25" t="n">
         <v>15</v>
@@ -4982,10 +5049,10 @@
         <v>19</v>
       </c>
       <c r="AW25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F26" t="n">
         <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>0.679</v>
+        <v>0.673</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="J26" t="n">
-        <v>88</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L26" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.381</v>
+        <v>0.379</v>
       </c>
       <c r="O26" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P26" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.822</v>
+        <v>0.82</v>
       </c>
       <c r="R26" t="n">
         <v>12.7</v>
@@ -5080,7 +5147,7 @@
         <v>46.1</v>
       </c>
       <c r="U26" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V26" t="n">
         <v>13.7</v>
@@ -5089,25 +5156,25 @@
         <v>5.5</v>
       </c>
       <c r="X26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB26" t="n">
         <v>107.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
@@ -5119,7 +5186,7 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5128,16 +5195,16 @@
         <v>2</v>
       </c>
       <c r="AK26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
       </c>
       <c r="AM26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN26" t="n">
         <v>4</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>3</v>
       </c>
       <c r="AO26" t="n">
         <v>6</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
         <v>6</v>
@@ -5158,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="AU26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5167,13 +5234,13 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA26" t="n">
         <v>15</v>
@@ -5182,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="BC26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -5211,46 +5278,46 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F27" t="n">
         <v>36</v>
       </c>
       <c r="G27" t="n">
-        <v>0.357</v>
+        <v>0.345</v>
       </c>
       <c r="H27" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I27" t="n">
         <v>37.1</v>
       </c>
       <c r="J27" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L27" t="n">
         <v>6.6</v>
       </c>
       <c r="M27" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.346</v>
+        <v>0.345</v>
       </c>
       <c r="O27" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="P27" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
       <c r="R27" t="n">
         <v>11.9</v>
@@ -5265,13 +5332,13 @@
         <v>19.3</v>
       </c>
       <c r="V27" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W27" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X27" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" t="n">
         <v>5.6</v>
@@ -5280,16 +5347,16 @@
         <v>22.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.3</v>
+        <v>101.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>-1.9</v>
+        <v>-2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5301,7 +5368,7 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI27" t="n">
         <v>19</v>
@@ -5313,13 +5380,13 @@
         <v>17</v>
       </c>
       <c r="AL27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM27" t="n">
         <v>24</v>
       </c>
-      <c r="AM27" t="n">
-        <v>25</v>
-      </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5334,7 +5401,7 @@
         <v>9</v>
       </c>
       <c r="AS27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT27" t="n">
         <v>12</v>
@@ -5343,13 +5410,13 @@
         <v>29</v>
       </c>
       <c r="AV27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW27" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AY27" t="n">
         <v>24</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>5.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5489,13 +5556,13 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM28" t="n">
         <v>19</v>
@@ -5510,7 +5577,7 @@
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5525,13 +5592,13 @@
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW28" t="n">
         <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY28" t="n">
         <v>18</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -5575,43 +5642,43 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F29" t="n">
         <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>0.554</v>
+        <v>0.545</v>
       </c>
       <c r="H29" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3</v>
+        <v>82.7</v>
       </c>
       <c r="K29" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L29" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O29" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P29" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="Q29" t="n">
         <v>0.775</v>
@@ -5620,19 +5687,19 @@
         <v>11.9</v>
       </c>
       <c r="S29" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="T29" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U29" t="n">
         <v>21</v>
       </c>
       <c r="V29" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="W29" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X29" t="n">
         <v>4.3</v>
@@ -5647,16 +5714,16 @@
         <v>21.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF29" t="n">
         <v>12</v>
@@ -5665,16 +5732,16 @@
         <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
         <v>10</v>
@@ -5686,28 +5753,28 @@
         <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ29" t="n">
         <v>9</v>
       </c>
       <c r="AR29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS29" t="n">
         <v>21</v>
       </c>
       <c r="AT29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW29" t="n">
         <v>25</v>
@@ -5719,7 +5786,7 @@
         <v>14</v>
       </c>
       <c r="AZ29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA29" t="n">
         <v>6</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>-6.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF30" t="n">
         <v>24</v>
       </c>
       <c r="AG30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
@@ -5856,10 +5923,10 @@
         <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
@@ -5889,7 +5956,7 @@
         <v>28</v>
       </c>
       <c r="AV30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW30" t="n">
         <v>26</v>
@@ -5904,7 +5971,7 @@
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F31" t="n">
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.491</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
@@ -5957,10 +6024,10 @@
         <v>38.1</v>
       </c>
       <c r="J31" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L31" t="n">
         <v>7.8</v>
@@ -5969,31 +6036,31 @@
         <v>20.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.38</v>
+        <v>0.379</v>
       </c>
       <c r="O31" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P31" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
       <c r="R31" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T31" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U31" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V31" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="W31" t="n">
         <v>8.6</v>
@@ -6002,22 +6069,22 @@
         <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6038,7 +6105,7 @@
         <v>8</v>
       </c>
       <c r="AK31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL31" t="n">
         <v>15</v>
@@ -6047,31 +6114,31 @@
         <v>18</v>
       </c>
       <c r="AN31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
         <v>24</v>
       </c>
       <c r="AR31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT31" t="n">
         <v>19</v>
       </c>
-      <c r="AS31" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>17</v>
-      </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW31" t="n">
         <v>7</v>
@@ -6086,13 +6153,13 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-23-2013-14</t>
+          <t>2014-02-23</t>
         </is>
       </c>
     </row>
